--- a/data/trending_integrated_20261020_15.xlsx
+++ b/data/trending_integrated_20261020_15.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72900</v>
+        <v>3280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+13.02%</t>
+          <t>'+12.52%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="G2" t="n">
-        <v>234</v>
+        <v>694</v>
       </c>
       <c r="H2" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K2" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L2" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M2" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N2" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>150469777900</v>
+        <v>67543625948</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-17000</v>
+        <v>-831000</v>
       </c>
       <c r="S2" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
+          <t>김정은 사망설에 따른 급등. 북한 관련 지정학적 리스크 부각 및 관련주로 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '목표가']</t>
+          <t>['김정은', '사망설', '지정학']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,91 +643,91 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>72400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.15%</t>
+          <t>'+12.25%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="F3" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>596</v>
+        <v>236</v>
       </c>
       <c r="H3" t="n">
-        <v>0.73</v>
+        <v>5.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2915</v>
+        <v>64500</v>
       </c>
       <c r="K3" t="n">
-        <v>2920</v>
+        <v>68000</v>
       </c>
       <c r="L3" t="n">
-        <v>3445</v>
+        <v>79300</v>
       </c>
       <c r="M3" t="n">
-        <v>2875</v>
+        <v>66700</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>65252404350</v>
+        <v>152262588800</v>
       </c>
       <c r="P3" t="n">
-        <v>7050</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2500</v>
+        <v>17780</v>
       </c>
       <c r="R3" t="n">
-        <v>-831000</v>
+        <v>-17000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 사망설 등 지정학적 리스크 관련 루머 확산. 해당 루머를 통한 주가 변동 가능성 언급.</t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은', '사망설', '지정학적 리스크']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9730</v>
+        <v>9700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.69%</t>
+          <t>'+6.36%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F4" t="n">
         <v>146</v>
       </c>
       <c r="G4" t="n">
-        <v>655</v>
+        <v>677</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>259502153895</v>
+        <v>262282449110</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 테마 연계 가능성 언급. 신고가 돌파 및 단기 급등에 대한 긍정적 전망.</t>
+          <t>로봇, ESS, 이차전지 테마 연관성에 대한 긍정적 언급. 신고가 경신 및 조단위 시총 목표 가능성에 대한 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['로봇', '신고가', '시총']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3985</v>
+        <v>3980</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.27%</t>
+          <t>'+6.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>44</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>48514614832</v>
+        <v>48851462100</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16290</v>
+        <v>16310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+0.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G6" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H6" t="n">
         <v>2.03</v>
@@ -978,7 +978,7 @@
         <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>67218852160</v>
+        <v>68059049280</v>
       </c>
       <c r="P6" t="n">
         <v>62100</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>종목 부진 및 보호예수 물량에 대한 우려 표출. 타 종목과의 비교 언급.</t>
+          <t>피지컬 AI 로봇 직접 생산 및 빅웨이브와의 비교 언급. 소액주주 권익 보호 및 금감원 신고 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보호예수', '종목 부진', '쓰레기 종목']</t>
+          <t>['로봇', 'AI', '소액주주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43050</v>
+        <v>43000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="H7" t="n">
         <v>13.11</v>
@@ -1070,7 +1070,7 @@
         <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>16439586500</v>
+        <v>17036367000</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 발표 및 담관암 FDA 승인에 대한 기대감 표출. 클래스 1 가능성 언급.</t>
+          <t>C1 클래스 발표에 대한 기대감. 담관암 FDA 승인 가능성에 대한 긍정적 전망 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '클래스 1']</t>
+          <t>['C1', 'FDA', '승인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>12224561765</v>
+        <v>12799730490</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210500</v>
+        <v>210000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G9" t="n">
-        <v>1502</v>
+        <v>1488</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2752922843250</v>
+        <v>2852972159000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 논란 및 한국 증시 저평가 주장. 반도체 산업 성장성에 대한 부정적 언급.</t>
+          <t>정치적 이슈에 대한 부정적 언급 및 한국 증시 저평가 주장. 반도체 성장성에 대한 비관적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '정치', '저평가']</t>
+          <t>['저평가', '반도체', '증시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1219000</v>
+        <v>1212000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-5.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G10" t="n">
-        <v>1803</v>
+        <v>1791</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3529352978500</v>
+        <v>3626645757500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 중복 상장 관련 총수 이득, 주주 손해 논란. 정치적 이슈와 연계된 부정적 의견 다수.</t>
+          <t>정부와 정치인에 대한 강한 비난과 함께 SK하이닉스 주가 하락의 원인으로 지목. 최태원 회장의 솔리다임 상장 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '주가조작']</t>
+          <t>['주가조작', '정부', '상장']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2560</v>
+        <v>14140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-5.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="H11" t="n">
-        <v>1.14</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2695</v>
+        <v>14950</v>
       </c>
       <c r="K11" t="n">
-        <v>2645</v>
+        <v>14610</v>
       </c>
       <c r="L11" t="n">
-        <v>2715</v>
+        <v>14940</v>
       </c>
       <c r="M11" t="n">
-        <v>2510</v>
+        <v>14100</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>31465433595</v>
+        <v>25757237575</v>
       </c>
       <c r="P11" t="n">
-        <v>2755</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>51000</v>
+        <v>-106000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-57000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14160</v>
+        <v>17300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.28%</t>
+          <t>'-5.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>201</v>
+        <v>314</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K12" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L12" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M12" t="n">
-        <v>14100</v>
+        <v>17280</v>
       </c>
       <c r="N12" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>24740817555</v>
+        <v>50052428930</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-106000</v>
+        <v>-285000</v>
       </c>
       <c r="S12" t="n">
-        <v>-57000</v>
+        <v>-201000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17330</v>
+        <v>2545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-5.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>303</v>
+        <v>179</v>
       </c>
       <c r="H13" t="n">
-        <v>27.78</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18300</v>
+        <v>2695</v>
       </c>
       <c r="K13" t="n">
-        <v>18140</v>
+        <v>2645</v>
       </c>
       <c r="L13" t="n">
-        <v>18140</v>
+        <v>2715</v>
       </c>
       <c r="M13" t="n">
-        <v>17280</v>
+        <v>2510</v>
       </c>
       <c r="N13" t="n">
-        <v>27.85</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>47032701385</v>
+        <v>31810630265</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>2755</v>
       </c>
       <c r="Q13" t="n">
-        <v>17210</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>-285000</v>
+        <v>51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-201000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선업', '정부정책', '수주']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18250</v>
+        <v>18130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.41%</t>
+          <t>'-8.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
         <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1714,7 +1714,7 @@
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>104785913300</v>
+        <v>105682206270</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 매물대 형성, 개미 무덤 차트 패턴 언급. 기술력 부재 및 홍보성 상승에 대한 부정적 시각.</t>
+          <t>개인 물량 넘기기 및 개미 무덤 차트 생성에 대한 부정적 전망. 정책 관련 불확실성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['개미 무덤', '매물대', '기술력']</t>
+          <t>['개미', '차트', '보안']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>30600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.57%</t>
+          <t>'-9.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1800,13 +1800,13 @@
         <v>34150</v>
       </c>
       <c r="M15" t="n">
-        <v>30600</v>
+        <v>30550</v>
       </c>
       <c r="N15" t="n">
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>70408021000</v>
+        <v>72504015900</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.35%</t>
+          <t>'-10.41%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F16" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G16" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>72992271372</v>
+        <v>73308296778</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8590</v>
+        <v>8580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.63%</t>
+          <t>'-11.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17994685805</v>
+        <v>18122439575</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>70700</v>
+        <v>7690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.78%</t>
+          <t>'-13.98%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>926</v>
+        <v>181</v>
       </c>
       <c r="H18" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M18" t="n">
-        <v>70000</v>
+        <v>7600</v>
       </c>
       <c r="N18" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>125858473150</v>
+        <v>22173941020</v>
       </c>
       <c r="P18" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q18" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-628000</v>
+        <v>-86000</v>
       </c>
       <c r="S18" t="n">
-        <v>-70000</v>
+        <v>-48000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '급락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7660</v>
+        <v>70500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-14.32%</t>
+          <t>'-14.02%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>276</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="G19" t="n">
-        <v>177</v>
+        <v>935</v>
       </c>
       <c r="H19" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K19" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L19" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M19" t="n">
-        <v>7600</v>
+        <v>70000</v>
       </c>
       <c r="N19" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>21343354835</v>
+        <v>129363086200</v>
       </c>
       <c r="P19" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q19" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R19" t="n">
-        <v>-86000</v>
+        <v>-628000</v>
       </c>
       <c r="S19" t="n">
-        <v>-48000</v>
+        <v>-70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '정치', '급락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_15.xlsx
+++ b/data/trending_integrated_20261020_15.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3280</v>
+        <v>72500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.52%</t>
+          <t>'+12.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>694</v>
+        <v>239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>5.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2915</v>
+        <v>64500</v>
       </c>
       <c r="K2" t="n">
-        <v>2920</v>
+        <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>3445</v>
+        <v>79300</v>
       </c>
       <c r="M2" t="n">
-        <v>2875</v>
+        <v>66700</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>67543625948</v>
+        <v>153969626900</v>
       </c>
       <c r="P2" t="n">
-        <v>7050</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2500</v>
+        <v>17780</v>
       </c>
       <c r="R2" t="n">
-        <v>-831000</v>
+        <v>-17000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 사망설에 따른 급등. 북한 관련 지정학적 리스크 부각 및 관련주로 언급.</t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '사망설', '지정학']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,91 +643,91 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72400</v>
+        <v>3245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.25%</t>
+          <t>'+11.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="G3" t="n">
-        <v>236</v>
+        <v>712</v>
       </c>
       <c r="H3" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K3" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L3" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M3" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>152262588800</v>
+        <v>69506756638</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q3" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R3" t="n">
-        <v>-17000</v>
+        <v>-831000</v>
       </c>
       <c r="S3" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
+          <t>김정은 사망설 확산에 따른 급등 기대감이 형성되어 있으며, 관련 보도와 과거 사례를 근거로 추측하고 있음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '목표가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9700</v>
+        <v>9770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.36%</t>
+          <t>'+7.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G4" t="n">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>262282449110</v>
+        <v>264234654785</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3980</v>
+        <v>4005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.13%</t>
+          <t>'+6.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
         <v>44</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>48851462100</v>
+        <v>49160213453</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16310</v>
+        <v>16250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F6" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" t="n">
         <v>2.03</v>
@@ -978,7 +978,7 @@
         <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>68059049280</v>
+        <v>68995303375</v>
       </c>
       <c r="P6" t="n">
         <v>62100</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>피지컬 AI 로봇 직접 생산 및 빅웨이브와의 비교 언급. 소액주주 권익 보호 및 금감원 신고 관련 언급.</t>
+          <t>보호 예수 물량 해소와 주가 하락에 대한 우려가 있으며, 타 종목과의 비교, 피지컬AI 로봇 관련 언급이 있으나 투자 근거는 미약함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', 'AI', '소액주주']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43000</v>
+        <v>43050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G7" t="n">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="H7" t="n">
         <v>13.11</v>
@@ -1070,7 +1070,7 @@
         <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>17036367000</v>
+        <v>17678016450</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 클래스 발표에 대한 기대감. 담관암 FDA 승인 가능성에 대한 긍정적 전망 및 주가 상승 기대.</t>
+          <t>C1 클래스 발표에 대한 기대감이 높으며, 외인 및 기관의 연속 매수세와 과거 사례 분석을 기반으로 긍정적인 전망을 제시하고 있음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1', 'FDA', '승인']</t>
+          <t>['C1', '클래스1', 'FDA승인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7250</v>
+        <v>7290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
         <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>12799730490</v>
+        <v>13562924080</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210000</v>
+        <v>211000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="G9" t="n">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2852972159000</v>
+        <v>2967893440750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급 및 한국 증시 저평가 주장. 반도체 성장성에 대한 비관적 전망.</t>
+          <t>주요 내용이 정치적 비난 및 정치인 탄핵 요구로 구성되어 있어, 투자와 관련된 객관적 정보는 부재함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['저평가', '반도체', '증시']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1212000</v>
+        <v>1216000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.09%</t>
+          <t>'-4.78%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G10" t="n">
-        <v>1791</v>
+        <v>1920</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3626645757500</v>
+        <v>3751477936500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정부와 정치인에 대한 강한 비난과 함께 SK하이닉스 주가 하락의 원인으로 지목. 최태원 회장의 솔리다임 상장 관련 부정적 언급.</t>
+          <t>정치적 불만과 정부 비난이 주를 이루며, 주가 조작 의혹 제기 외에는 객관적인 투자 정보가 부족함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가조작', '정부', '상장']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14140</v>
+        <v>17320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-5.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>209</v>
+        <v>327</v>
       </c>
       <c r="H11" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K11" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L11" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M11" t="n">
-        <v>14100</v>
+        <v>17270</v>
       </c>
       <c r="N11" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>25757237575</v>
+        <v>53842023510</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-106000</v>
+        <v>-285000</v>
       </c>
       <c r="S11" t="n">
-        <v>-57000</v>
+        <v>-201000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17300</v>
+        <v>14140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-5.42%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K12" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L12" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M12" t="n">
-        <v>17280</v>
+        <v>14100</v>
       </c>
       <c r="N12" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>50052428930</v>
+        <v>26711450085</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-285000</v>
+        <v>-106000</v>
       </c>
       <c r="S12" t="n">
-        <v>-201000</v>
+        <v>-57000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업', '정부정책', '수주']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-5.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1622,7 +1622,7 @@
         <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>31810630265</v>
+        <v>32125625796</v>
       </c>
       <c r="P13" t="n">
         <v>2755</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18130</v>
+        <v>18180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.02%</t>
+          <t>'-7.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F14" t="n">
         <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1714,7 +1714,7 @@
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>105682206270</v>
+        <v>106266277845</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개인 물량 넘기기 및 개미 무덤 차트 생성에 대한 부정적 전망. 정책 관련 불확실성 언급.</t>
+          <t>개인 투자자들의 매도 및 물량 넘기기, 차트 분석을 통한 하락 전망이 주를 이루며, 정책 관련 언급은 있으나 구체성이 부족함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['개미', '차트', '보안']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30600</v>
+        <v>30650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.87%</t>
+          <t>'-9.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" t="n">
         <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1800,13 +1800,13 @@
         <v>34150</v>
       </c>
       <c r="M15" t="n">
-        <v>30550</v>
+        <v>30500</v>
       </c>
       <c r="N15" t="n">
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>72504015900</v>
+        <v>73983503650</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.41%</t>
+          <t>'-10.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F16" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>73308296778</v>
+        <v>73521962102</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8580</v>
+        <v>8570</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.73%</t>
+          <t>'-11.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>18122439575</v>
+        <v>18274848465</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>테슬라 부품 공급 관련 언급 및 주주환원 부족 지적. 공매도 관련 부정적 예측.</t>
+          <t>주주 환원 정책 부재 언급이 있으나, 전반적으로 주가 급등락에 대한 개인 투자자들의 불안감과 기대감이 혼재된 의견이 많음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['테슬라', '주주환원', '공매도']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7690</v>
+        <v>7730</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.98%</t>
+          <t>'-13.53%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
         <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H18" t="n">
         <v>36.01</v>
@@ -2082,7 +2082,7 @@
         <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>22173941020</v>
+        <v>22371692900</v>
       </c>
       <c r="P18" t="n">
         <v>19150</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70500</v>
+        <v>70700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-14.02%</t>
+          <t>'-13.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F19" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G19" t="n">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="H19" t="n">
         <v>9.380000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>129363086200</v>
+        <v>131807617950</v>
       </c>
       <c r="P19" t="n">
         <v>184000</v>

--- a/data/trending_integrated_20261020_15.xlsx
+++ b/data/trending_integrated_20261020_15.xlsx
@@ -584,7 +584,7 @@
         <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>153969626900</v>
+        <v>154865436900</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3245</v>
+        <v>3235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.32%</t>
+          <t>'+10.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="F3" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
-        <v>712</v>
+        <v>782</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>69506756638</v>
+        <v>69849424013</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 사망설 확산에 따른 급등 기대감이 형성되어 있으며, 관련 보도와 과거 사례를 근거로 추측하고 있음.</t>
+          <t>김정은 사망설 등 지정학적 이슈로 인한 급등 기대감. 북한 관련 정책 및 군사적 긴장감 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['김정은 사망설', '지정학적 이슈', '급등 기대감']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G4" t="n">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>264234654785</v>
+        <v>265158349665</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 테마 연관성에 대한 긍정적 언급. 신고가 경신 및 조단위 시총 목표 가능성에 대한 기대.</t>
+          <t>로봇, ESS, 2차전지 등 복합 섹터 포함으로 인한 강한 상승 기대감. 신고가 경신 및 임원 매수 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '신고가', '시총']</t>
+          <t>['로봇', 'ESS', '2차전지']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.80%</t>
+          <t>'+6.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>44</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>49160213453</v>
+        <v>49306965453</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -978,7 +978,7 @@
         <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>68995303375</v>
+        <v>69141845875</v>
       </c>
       <c r="P6" t="n">
         <v>62100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43050</v>
+        <v>43000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F7" t="n">
         <v>119</v>
       </c>
       <c r="G7" t="n">
-        <v>1289</v>
+        <v>1318</v>
       </c>
       <c r="H7" t="n">
         <v>13.11</v>
@@ -1070,7 +1070,7 @@
         <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>17678016450</v>
+        <v>17919547450</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 클래스 발표에 대한 기대감이 높으며, 외인 및 기관의 연속 매수세와 과거 사례 분석을 기반으로 긍정적인 전망을 제시하고 있음.</t>
+          <t>FDA C1 클래스 발표에 대한 기대감. 외인 및 기관 매수세 유입과 함께 주가 상승 가능성 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1', '클래스1', 'FDA승인']</t>
+          <t>['FDA C1', '기대감', '외인 기관 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7290</v>
+        <v>7270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
         <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>13562924080</v>
+        <v>14546257010</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211000</v>
+        <v>211500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-2.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G9" t="n">
-        <v>1483</v>
+        <v>1463</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2967893440750</v>
+        <v>3188052462250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주요 내용이 정치적 비난 및 정치인 탄핵 요구로 구성되어 있어, 투자와 관련된 객관적 정보는 부재함.</t>
+          <t>국내 정치 이슈와 연계된 부정적 심리 확산. 반도체 성장 전망에 대한 회의론 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치 이슈', '안보 불안', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1216000</v>
+        <v>1223000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-4.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G10" t="n">
-        <v>1920</v>
+        <v>2009</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3751477936500</v>
+        <v>4015943125500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 불만과 정부 비난이 주를 이루며, 주가 조작 의혹 제기 외에는 객관적인 투자 정보가 부족함.</t>
+          <t>정치적 이슈 및 경영진 관련 루머로 인한 하락 심리. 솔리다임 상장 이슈 및 주가조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치 이슈', '솔리다임', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17320</v>
+        <v>14160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.36%</t>
+          <t>'-5.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F11" t="n">
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K11" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L11" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M11" t="n">
-        <v>17270</v>
+        <v>14100</v>
       </c>
       <c r="N11" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>53842023510</v>
+        <v>27078477285</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-285000</v>
+        <v>-106000</v>
       </c>
       <c r="S11" t="n">
-        <v>-201000</v>
+        <v>-57000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
+          <t>정치적 발언 및 공매도 관련 부정적 의견. 실적 개선 기대감과 주가 조작 의혹 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업', '정부정책', '수주']</t>
+          <t>['공매도', '정치적 발언', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14140</v>
+        <v>17320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-5.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>213</v>
+        <v>340</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K12" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L12" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M12" t="n">
-        <v>14100</v>
+        <v>17270</v>
       </c>
       <c r="N12" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>26711450085</v>
+        <v>57747129270</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-106000</v>
+        <v>-285000</v>
       </c>
       <c r="S12" t="n">
-        <v>-57000</v>
+        <v>-201000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
         <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H13" t="n">
         <v>1.14</v>
@@ -1622,7 +1622,7 @@
         <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>32125625796</v>
+        <v>32359950956</v>
       </c>
       <c r="P13" t="n">
         <v>2755</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18180</v>
+        <v>18170</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.76%</t>
+          <t>'-7.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
         <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1714,7 +1714,7 @@
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>106266277845</v>
+        <v>106573587055</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30650</v>
+        <v>30550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.72%</t>
+          <t>'-10.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>73983503650</v>
+        <v>74774565350</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.13%</t>
+          <t>'-10.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F16" t="n">
         <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>73521962102</v>
+        <v>73782428880</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 및 거래량 증가 확인. 2연상 기대감 존재.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 전망. 글로벌 강관 기술력 입증 및 외인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '거래량']</t>
+          <t>['스페이스X', '호재 공시', '강관 기술']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8570</v>
+        <v>8650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.83%</t>
+          <t>'-11.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
         <v>397</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>18274848465</v>
+        <v>18445452415</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7730</v>
+        <v>70600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.53%</t>
+          <t>'-13.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>283</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>986</v>
       </c>
       <c r="H18" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K18" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L18" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M18" t="n">
-        <v>7600</v>
+        <v>70000</v>
       </c>
       <c r="N18" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>22371692900</v>
+        <v>133726878950</v>
       </c>
       <c r="P18" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R18" t="n">
-        <v>-86000</v>
+        <v>-628000</v>
       </c>
       <c r="S18" t="n">
-        <v>-48000</v>
+        <v>-70000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '정치', '급락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70700</v>
+        <v>7690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.78%</t>
+          <t>'-13.98%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>946</v>
+        <v>187</v>
       </c>
       <c r="H19" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L19" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M19" t="n">
-        <v>70000</v>
+        <v>7600</v>
       </c>
       <c r="N19" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>131807617950</v>
+        <v>22437980700</v>
       </c>
       <c r="P19" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q19" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R19" t="n">
-        <v>-628000</v>
+        <v>-86000</v>
       </c>
       <c r="S19" t="n">
-        <v>-70000</v>
+        <v>-48000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '급락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_15.xlsx
+++ b/data/trending_integrated_20261020_15.xlsx
@@ -584,7 +584,7 @@
         <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>154865436900</v>
+        <v>154866524400</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -670,13 +670,13 @@
         <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G3" t="n">
-        <v>782</v>
+        <v>819</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>69849424013</v>
+        <v>69860930908</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 사망설 등 지정학적 이슈로 인한 급등 기대감. 북한 관련 정책 및 군사적 긴장감 부각.</t>
+          <t>김정은 사망설 확산에 따른 지정학적 리스크 부각 및 급등 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '지정학적 이슈', '급등 기대감']</t>
+          <t>['김정은', '사망설', '빅텍']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F4" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G4" t="n">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>265158349665</v>
+        <v>265197585985</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>49306965453</v>
+        <v>49311481453</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -946,13 +946,13 @@
         <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H6" t="n">
         <v>2.03</v>
@@ -978,7 +978,7 @@
         <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>69141845875</v>
+        <v>69155967125</v>
       </c>
       <c r="P6" t="n">
         <v>62100</v>
@@ -1038,13 +1038,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F7" t="n">
         <v>119</v>
       </c>
       <c r="G7" t="n">
-        <v>1318</v>
+        <v>1335</v>
       </c>
       <c r="H7" t="n">
         <v>13.11</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FDA C1 클래스 발표에 대한 기대감. 외인 및 기관 매수세 유입과 함께 주가 상승 가능성 논의.</t>
+          <t>HLB 간암 신약 FDA 허가 기대감 및 C1 클래스 발표 임박, 외인/기관 동시 매수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA C1', '기대감', '외인 기관 매수']</t>
+          <t>['HLB', 'FDA', '간암신약']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>14546257010</v>
+        <v>14546511460</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="G9" t="n">
-        <v>1463</v>
+        <v>1502</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3188052462250</v>
+        <v>3188497881250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내 정치 이슈와 연계된 부정적 심리 확산. 반도체 성장 전망에 대한 회의론 제기.</t>
+          <t>이재명 관련 정치적 이슈와 반도체 산업 성장 둔화 우려로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치 이슈', '안보 불안', '반도체']</t>
+          <t>['이재명', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G10" t="n">
-        <v>2009</v>
+        <v>2088</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>4015943125500</v>
+        <v>4019772338500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 경영진 관련 루머로 인한 하락 심리. 솔리다임 상장 이슈 및 주가조작 의혹 제기.</t>
+          <t>솔리다임 상장 이슈와 정치적 논란으로 인한 주가 하락 우려, 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치 이슈', '솔리다임', '주가조작']</t>
+          <t>['솔리다임', '최태원', '이재명']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,10 +1406,10 @@
         <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
         <v>217</v>
@@ -1438,7 +1438,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>27078477285</v>
+        <v>27087100725</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1498,13 +1498,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F12" t="n">
         <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>57747129270</v>
+        <v>57747302470</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1590,13 +1590,13 @@
         <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
         <v>1.14</v>
@@ -1622,7 +1622,7 @@
         <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>32359950956</v>
+        <v>32371190456</v>
       </c>
       <c r="P13" t="n">
         <v>2755</v>
@@ -1682,13 +1682,13 @@
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1714,7 +1714,7 @@
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>106573587055</v>
+        <v>106577202885</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1759,11 +1759,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30550</v>
+        <v>1573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1771,19 +1771,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="H15" t="n">
-        <v>12.79</v>
+        <v>1.77</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,71 +1791,71 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>33950</v>
+        <v>1748</v>
       </c>
       <c r="K15" t="n">
-        <v>33250</v>
+        <v>1706</v>
       </c>
       <c r="L15" t="n">
-        <v>34150</v>
+        <v>1895</v>
       </c>
       <c r="M15" t="n">
-        <v>30500</v>
+        <v>1555</v>
       </c>
       <c r="N15" t="n">
-        <v>12.81</v>
+        <v>0.83</v>
       </c>
       <c r="O15" t="n">
-        <v>74774565350</v>
+        <v>73788588748</v>
       </c>
       <c r="P15" t="n">
-        <v>59300</v>
+        <v>2970</v>
       </c>
       <c r="Q15" t="n">
-        <v>22000</v>
+        <v>890</v>
       </c>
       <c r="R15" t="n">
-        <v>-430000</v>
+        <v>-798000</v>
       </c>
       <c r="S15" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
+          <t>스페이스X 계약 공시 기반 급등세, 2연상 기대감 및 글로벌 기술력 입증.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['태양광', '공매도', '시장 하락']</t>
+          <t>['스페이스X', '호재공시', '철강']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1573</v>
+        <v>30550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1863,19 +1863,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>234</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="H16" t="n">
-        <v>1.77</v>
+        <v>12.79</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1748</v>
+        <v>33950</v>
       </c>
       <c r="K16" t="n">
-        <v>1706</v>
+        <v>33250</v>
       </c>
       <c r="L16" t="n">
-        <v>1895</v>
+        <v>34150</v>
       </c>
       <c r="M16" t="n">
-        <v>1555</v>
+        <v>30500</v>
       </c>
       <c r="N16" t="n">
-        <v>0.83</v>
+        <v>12.81</v>
       </c>
       <c r="O16" t="n">
-        <v>73782428880</v>
+        <v>74811989100</v>
       </c>
       <c r="P16" t="n">
-        <v>2970</v>
+        <v>59300</v>
       </c>
       <c r="Q16" t="n">
-        <v>890</v>
+        <v>22000</v>
       </c>
       <c r="R16" t="n">
-        <v>-798000</v>
+        <v>-430000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등세 전망. 글로벌 강관 기술력 입증 및 외인 매수세 유입 확인.</t>
+          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '강관 기술']</t>
+          <t>['태양광', '공매도', '시장 하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F17" t="n">
         <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>18445452415</v>
+        <v>18445461065</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주 환원 정책 부재 언급이 있으나, 전반적으로 주가 급등락에 대한 개인 투자자들의 불안감과 기대감이 혼재된 의견이 많음.</t>
+          <t>테슬라 부품 공급 및 중복 상장 관련 논란, 주주환원 부재로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['테슬라', '중복상장', '주주환원']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F18" t="n">
         <v>150</v>
       </c>
       <c r="G18" t="n">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="H18" t="n">
         <v>9.380000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>133726878950</v>
+        <v>133731185550</v>
       </c>
       <c r="P18" t="n">
         <v>184000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+          <t>공매도 물량 증가 및 정치적 이슈로 인한 주가 하락, 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '급락']</t>
+          <t>['공매도', '정치', '한화시스템']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,10 +2142,10 @@
         <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
         <v>187</v>
@@ -2174,7 +2174,7 @@
         <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>22437980700</v>
+        <v>22450307770</v>
       </c>
       <c r="P19" t="n">
         <v>19150</v>
